--- a/forms/trg/Formulir_TRG_ph-entomology.xlsx
+++ b/forms/trg/Formulir_TRG_ph-entomology.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Perlindungan tanaman (hama &amp; penyakit)</t>
+          <t>Penyakit menular, vaksin &amp; resistensi</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="6">
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Penyakit menular, vaksin &amp; resistensi</t>
+          <t>Perlindungan tanaman (hama &amp; penyakit)</t>
         </is>
       </c>
     </row>

--- a/forms/trg/Formulir_TRG_ph-entomology.xlsx
+++ b/forms/trg/Formulir_TRG_ph-entomology.xlsx
@@ -949,7 +949,11 @@
           <t>Dr. Erniwati Ibrahim, SKM., M.Kes</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
@@ -1399,7 +1403,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Penyakit menular, vaksin &amp; resistensi</t>
+          <t>Perlindungan tanaman (hama &amp; penyakit)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1411,7 +1415,7 @@
     <row r="6">
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Perlindungan tanaman (hama &amp; penyakit)</t>
+          <t>Penyakit menular, vaksin &amp; resistensi</t>
         </is>
       </c>
     </row>
